--- a/AdmxEmprd.xlsx
+++ b/AdmxEmprd.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19A86941-F669-4C09-A76D-F40B4DA271D4}"/>
+  <xr:revisionPtr revIDLastSave="358" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0364B0EC-A21C-4BF3-9261-B869E3606F95}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA07F2F2-64A9-422B-A346-649C5134B655}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="71">
   <si>
     <t>ADM</t>
   </si>
@@ -68,9 +68,6 @@
     <t>2409 - MARIA BELTRÃO SALDANHA COELHO</t>
   </si>
   <si>
-    <t>2411 - JOÃO CARLOS BEHISNELIAN</t>
-  </si>
-  <si>
     <t>2504 - MARIA ANGÉLICA A. MONTEIRO DA COSTA</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>2507 - KATIA FERREIRA DE BARROS</t>
   </si>
   <si>
-    <t>2509 - RAFAEL CURSINO DE MOURA LEVY</t>
-  </si>
-  <si>
     <t>2510 - SAMAUMA EVENTOS LTDA</t>
   </si>
   <si>
@@ -113,9 +107,6 @@
     <t>EMPRD</t>
   </si>
   <si>
-    <t>2515 - MARCO FREIRE (ÁREA EXTERNA)</t>
-  </si>
-  <si>
     <t>2516 - JOSÉ CARLOS MORAES ABREU FILHO</t>
   </si>
   <si>
@@ -149,18 +140,12 @@
     <t>Matheus Sanches</t>
   </si>
   <si>
-    <t>Vitor Ramos</t>
-  </si>
-  <si>
     <t>julia.vigorito@osborne.com.br</t>
   </si>
   <si>
     <t>matheus.sanches@osborne.com.br</t>
   </si>
   <si>
-    <t>vitor.ramos@osborne.com.br</t>
-  </si>
-  <si>
     <t>Carolina Oliveira</t>
   </si>
   <si>
@@ -228,6 +213,45 @@
   </si>
   <si>
     <t>marcos.varjao@osborne.com.br</t>
+  </si>
+  <si>
+    <t>2602 - RENATA STUHLBERGER</t>
+  </si>
+  <si>
+    <t>2604 - ANDRE FRANCO SALES</t>
+  </si>
+  <si>
+    <t>felipe.schwartz@osborne.com.br</t>
+  </si>
+  <si>
+    <t>2606 - MARCO FREIRE (FAZENDA BOA VISTA)</t>
+  </si>
+  <si>
+    <t>Vitor Carvalho; Caio Fausto</t>
+  </si>
+  <si>
+    <t>vitor.carvalho@osborne.com.br; caio.fausto@osborne.com.br</t>
+  </si>
+  <si>
+    <t>2607 - DAN-DAN EMPREENDIMENTOS (LOJA 02)</t>
+  </si>
+  <si>
+    <t>2303 - LUIZ ROGÉRIO BERTO</t>
+  </si>
+  <si>
+    <t>2404 - LUIZ HENRIQUE FRAGA</t>
+  </si>
+  <si>
+    <t>2603 - FERNANDO AUGUSTO VASCONCELLOS</t>
+  </si>
+  <si>
+    <t>2213 - TOMAS DA VEIGA PEREIRA</t>
+  </si>
+  <si>
+    <t>2309 - BEATRIZ DO REGO NOVAES</t>
+  </si>
+  <si>
+    <t>2211 - DAN-DAN EMPREEND. IMOBILIÁRIOS</t>
   </si>
 </sst>
 </file>
@@ -335,7 +359,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -672,11 +707,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="40" style="3" customWidth="1"/>
+    <col min="2" max="2" width="47.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" style="4" customWidth="1"/>
     <col min="4" max="4" width="11.21875" style="4" customWidth="1"/>
     <col min="5" max="5" width="16" style="1" customWidth="1"/>
@@ -690,7 +725,7 @@
   <sheetData>
     <row r="1" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>3</v>
@@ -699,19 +734,19 @@
         <v>0</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>2212</v>
       </c>
@@ -719,22 +754,22 @@
         <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2409</v>
       </c>
@@ -742,213 +777,212 @@
         <v>8</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
+        <v>2603</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
         <v>2316</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
         <v>2504</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
-        <v>2509</v>
-      </c>
       <c r="B6" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>15</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>2510</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
-        <v>2515</v>
+        <v>2606</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>51</v>
+        <v>20</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>2506</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F9" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>58</v>
-      </c>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>2507</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>2505</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>2407</v>
       </c>
@@ -959,187 +993,319 @@
         <v>2</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>2511</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>2512</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>2516</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
+        <v>2602</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7">
+        <v>2604</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7">
         <v>2317</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B18" s="8" t="s">
         <v>6</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7">
-        <v>2514</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
-        <v>2411</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>9</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
-        <v>2601</v>
+        <v>2514</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7">
+        <v>2607</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7">
+        <v>2601</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7">
+        <v>2303</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+    </row>
+    <row r="23" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7">
+        <v>2404</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7">
+        <v>2213</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7">
+        <v>2309</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7">
+        <v>2211</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" xr:uid="{FF584219-8DDB-4AF7-ABB3-AEBC92C6AED5}"/>
-    <hyperlink ref="F6" r:id="rId2" xr:uid="{ADCA78C6-BD06-4E35-BDC7-DD5EB5EBF9DD}"/>
+    <hyperlink ref="F5" r:id="rId1" xr:uid="{FF584219-8DDB-4AF7-ABB3-AEBC92C6AED5}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" scale="91" orientation="landscape" r:id="rId3"/>
+  <pageSetup paperSize="9" scale="91" orientation="landscape" r:id="rId2"/>
 </worksheet>
 </file>
--- a/AdmxEmprd.xlsx
+++ b/AdmxEmprd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="358" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0364B0EC-A21C-4BF3-9261-B869E3606F95}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{305B39C0-B669-4945-B738-2EB99573D7E5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA07F2F2-64A9-422B-A346-649C5134B655}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="74">
   <si>
     <t>ADM</t>
   </si>
@@ -252,6 +252,15 @@
   </si>
   <si>
     <t>2211 - DAN-DAN EMPREEND. IMOBILIÁRIOS</t>
+  </si>
+  <si>
+    <t>2515 - MARCO FREIRE (ÁREA EXTERNA)</t>
+  </si>
+  <si>
+    <t>2509 - RAFAEL CURSINO DE MOURA LEVY</t>
+  </si>
+  <si>
+    <t>2411 - JOÃO CARLOS BEHISNELIAN</t>
   </si>
 </sst>
 </file>
@@ -707,14 +716,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="47.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" style="4" customWidth="1"/>
     <col min="4" max="4" width="11.21875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="31.88671875" style="1" customWidth="1"/>
     <col min="7" max="7" width="17.77734375" style="1" customWidth="1"/>
     <col min="8" max="8" width="45.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -746,7 +755,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>2212</v>
       </c>
@@ -769,7 +778,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2409</v>
       </c>
@@ -792,7 +801,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>2603</v>
       </c>
@@ -815,7 +824,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>2316</v>
       </c>
@@ -838,7 +847,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>2504</v>
       </c>
@@ -862,7 +871,7 @@
       </c>
       <c r="J6" s="9"/>
     </row>
-    <row r="7" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>2510</v>
       </c>
@@ -958,7 +967,7 @@
       </c>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>2505</v>
       </c>
@@ -982,7 +991,7 @@
       </c>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>2407</v>
       </c>
@@ -1006,7 +1015,7 @@
       </c>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>2511</v>
       </c>
@@ -1029,7 +1038,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>2512</v>
       </c>
@@ -1052,7 +1061,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>2516</v>
       </c>
@@ -1075,7 +1084,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>2602</v>
       </c>
@@ -1098,7 +1107,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:7" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>2604</v>
       </c>
@@ -1121,7 +1130,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>2317</v>
       </c>
@@ -1144,7 +1153,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:7" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>2514</v>
       </c>
@@ -1167,7 +1176,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="6" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>2607</v>
       </c>
@@ -1190,7 +1199,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>2601</v>
       </c>
@@ -1213,7 +1222,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>2303</v>
       </c>
@@ -1230,7 +1239,7 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>2404</v>
       </c>
@@ -1247,7 +1256,7 @@
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
     </row>
-    <row r="24" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>2213</v>
       </c>
@@ -1264,7 +1273,7 @@
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
     </row>
-    <row r="25" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>2309</v>
       </c>
@@ -1281,7 +1290,7 @@
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>2211</v>
       </c>
@@ -1297,6 +1306,57 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
+    </row>
+    <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7">
+        <v>2515</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
+        <v>2509</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+    </row>
+    <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
+        <v>2411</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">

--- a/AdmxEmprd.xlsx
+++ b/AdmxEmprd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="373" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{305B39C0-B669-4945-B738-2EB99573D7E5}"/>
+  <xr:revisionPtr revIDLastSave="379" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3BF86C7-5B9D-44E4-A027-8C670AAE3875}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA07F2F2-64A9-422B-A346-649C5134B655}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="75">
   <si>
     <t>ADM</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>2411 - JOÃO CARLOS BEHISNELIAN</t>
+  </si>
+  <si>
+    <t>2605 - ALESSANDRO ARDUINI</t>
   </si>
 </sst>
 </file>
@@ -716,7 +719,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="2" customWidth="1"/>
@@ -1341,7 +1344,7 @@
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
     </row>
-    <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>2411</v>
       </c>
@@ -1357,6 +1360,23 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7">
+        <v>2605</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">

--- a/AdmxEmprd.xlsx
+++ b/AdmxEmprd.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="379" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3BF86C7-5B9D-44E4-A027-8C670AAE3875}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF763863-1010-45B9-B0C6-F565773DC8C3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA07F2F2-64A9-422B-A346-649C5134B655}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{CA07F2F2-64A9-422B-A346-649C5134B655}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="78">
   <si>
     <t>ADM</t>
   </si>
@@ -264,6 +264,15 @@
   </si>
   <si>
     <t>2605 - ALESSANDRO ARDUINI</t>
+  </si>
+  <si>
+    <t>2611 - GUILHERME BOTTURA</t>
+  </si>
+  <si>
+    <t>251001 - LUIZ ANTONIO BETTIOL</t>
+  </si>
+  <si>
+    <t>222001 - GERSON NASCIMENTO (PÓS OBRA)</t>
   </si>
 </sst>
 </file>
@@ -393,10 +402,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -719,7 +724,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="2" customWidth="1"/>
@@ -760,480 +765,456 @@
     </row>
     <row r="2" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
-        <v>2212</v>
+        <v>2407</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
-        <v>2409</v>
+        <v>2511</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
-        <v>2603</v>
+        <v>2512</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
-        <v>2316</v>
+        <v>2516</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
-        <v>2504</v>
+        <v>2602</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J6" s="9"/>
     </row>
     <row r="7" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
-        <v>2510</v>
+        <v>2604</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="1:10" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>53</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
       <c r="J8" s="9"/>
     </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
-        <v>2506</v>
+        <v>2611</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>53</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
-        <v>2507</v>
+        <v>222001</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>53</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
       <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
-        <v>2505</v>
+        <v>2212</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
-        <v>2511</v>
+        <v>2603</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
-        <v>2512</v>
+        <v>2303</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>51</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
-        <v>2516</v>
+        <v>2316</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
-        <v>2602</v>
+        <v>2504</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
-        <v>2604</v>
+        <v>2510</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
-        <v>2317</v>
+        <v>2606</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>33</v>
+        <v>62</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
-        <v>2514</v>
+        <v>2506</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>34</v>
+        <v>47</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
-        <v>2607</v>
+        <v>2507</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>33</v>
+        <v>47</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
-        <v>2601</v>
+        <v>2404</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
-        <v>2303</v>
+        <v>2213</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>20</v>
@@ -1244,10 +1225,10 @@
     </row>
     <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
-        <v>2404</v>
+        <v>2309</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>13</v>
@@ -1261,10 +1242,10 @@
     </row>
     <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
-        <v>2213</v>
+        <v>2515</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>13</v>
@@ -1278,10 +1259,10 @@
     </row>
     <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
-        <v>2309</v>
+        <v>2509</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>13</v>
@@ -1295,16 +1276,16 @@
     </row>
     <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
-        <v>2211</v>
+        <v>251001</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -1312,44 +1293,56 @@
     </row>
     <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
-        <v>2515</v>
+        <v>2317</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
+        <v>18</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
-        <v>2509</v>
+        <v>2514</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
-        <v>2411</v>
+        <v>2607</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>1</v>
@@ -1357,33 +1350,102 @@
       <c r="D29" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-    </row>
-    <row r="30" spans="1:7" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E29" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
-        <v>2605</v>
+        <v>2601</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
+      <c r="E30" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7">
+        <v>2211</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7">
+        <v>2411</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+    </row>
+    <row r="33" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7">
+        <v>2505</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{FF584219-8DDB-4AF7-ABB3-AEBC92C6AED5}"/>
+    <hyperlink ref="F15" r:id="rId1" xr:uid="{FF584219-8DDB-4AF7-ABB3-AEBC92C6AED5}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="91" orientation="landscape" r:id="rId2"/>

--- a/AdmxEmprd.xlsx
+++ b/AdmxEmprd.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="423" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF763863-1010-45B9-B0C6-F565773DC8C3}"/>
+  <xr:revisionPtr revIDLastSave="430" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA9888D3-C261-40DE-8083-D51C6E899FF9}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{CA07F2F2-64A9-422B-A346-649C5134B655}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA07F2F2-64A9-422B-A346-649C5134B655}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="79">
   <si>
     <t>ADM</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>222001 - GERSON NASCIMENTO (PÓS OBRA)</t>
+  </si>
+  <si>
+    <t>2612 - FABIO DE BARROS PINHEIRO</t>
   </si>
 </sst>
 </file>
@@ -402,6 +405,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -724,7 +731,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="2" customWidth="1"/>
@@ -945,10 +952,10 @@
     </row>
     <row r="10" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
-        <v>222001</v>
+        <v>2612</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>2</v>
@@ -956,43 +963,37 @@
       <c r="D10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
-        <v>2212</v>
+        <v>222001</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>54</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
       <c r="J11" s="9"/>
     </row>
     <row r="12" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
-        <v>2409</v>
+        <v>2212</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>14</v>
@@ -1001,10 +1002,10 @@
         <v>20</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>54</v>
@@ -1013,10 +1014,10 @@
     </row>
     <row r="13" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
-        <v>2603</v>
+        <v>2409</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>14</v>
@@ -1033,13 +1034,14 @@
       <c r="G13" s="7" t="s">
         <v>54</v>
       </c>
+      <c r="J13" s="9"/>
     </row>
     <row r="14" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
-        <v>2303</v>
+        <v>2603</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>14</v>
@@ -1047,39 +1049,39 @@
       <c r="D14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="E14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="15" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
-        <v>2316</v>
+        <v>2303</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>53</v>
-      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:10" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
-        <v>2504</v>
+        <v>2316</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>13</v>
@@ -1088,10 +1090,10 @@
         <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>53</v>
@@ -1099,10 +1101,10 @@
     </row>
     <row r="17" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
-        <v>2510</v>
+        <v>2504</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>13</v>
@@ -1120,24 +1122,24 @@
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
-        <v>2606</v>
+        <v>2510</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>63</v>
+        <v>43</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>53</v>
@@ -1145,22 +1147,22 @@
     </row>
     <row r="19" spans="1:7" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
-        <v>2506</v>
+        <v>2606</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>53</v>
@@ -1168,10 +1170,10 @@
     </row>
     <row r="20" spans="1:7" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>13</v>
@@ -1189,12 +1191,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
-        <v>2404</v>
+        <v>2507</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>13</v>
@@ -1202,16 +1204,22 @@
       <c r="D21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="E21" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
-        <v>2213</v>
+        <v>2404</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>13</v>
@@ -1225,10 +1233,10 @@
     </row>
     <row r="23" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
-        <v>2309</v>
+        <v>2213</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>13</v>
@@ -1242,10 +1250,10 @@
     </row>
     <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
-        <v>2515</v>
+        <v>2309</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>13</v>
@@ -1259,10 +1267,10 @@
     </row>
     <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
-        <v>2509</v>
+        <v>2515</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>13</v>
@@ -1276,10 +1284,10 @@
     </row>
     <row r="26" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
-        <v>251001</v>
+        <v>2509</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>13</v>
@@ -1293,33 +1301,27 @@
     </row>
     <row r="27" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
-        <v>2317</v>
+        <v>251001</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>52</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
-        <v>2514</v>
+        <v>2317</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>1</v>
@@ -1328,10 +1330,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>52</v>
@@ -1339,10 +1341,10 @@
     </row>
     <row r="29" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
-        <v>2607</v>
+        <v>2514</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>1</v>
@@ -1351,10 +1353,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>52</v>
@@ -1362,10 +1364,10 @@
     </row>
     <row r="30" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
-        <v>2601</v>
+        <v>2607</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>1</v>
@@ -1374,10 +1376,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>52</v>
@@ -1385,10 +1387,10 @@
     </row>
     <row r="31" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
-        <v>2211</v>
+        <v>2601</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>1</v>
@@ -1396,16 +1398,22 @@
       <c r="D31" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+      <c r="E31" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="32" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
-        <v>2411</v>
+        <v>2211</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>1</v>
@@ -1419,24 +1427,41 @@
     </row>
     <row r="33" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
+        <v>2411</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7">
         <v>2505</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B34" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D34" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E34" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F34" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G34" s="7" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1445,7 +1470,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="F15" r:id="rId1" xr:uid="{FF584219-8DDB-4AF7-ABB3-AEBC92C6AED5}"/>
+    <hyperlink ref="F16" r:id="rId1" xr:uid="{FF584219-8DDB-4AF7-ABB3-AEBC92C6AED5}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" scale="91" orientation="landscape" r:id="rId2"/>

--- a/AdmxEmprd.xlsx
+++ b/AdmxEmprd.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="430" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA9888D3-C261-40DE-8083-D51C6E899FF9}"/>
+  <xr:revisionPtr revIDLastSave="437" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A5CF938-EF98-406D-88C4-C340A4DAE72E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA07F2F2-64A9-422B-A346-649C5134B655}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="80">
   <si>
     <t>ADM</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>2612 - FABIO DE BARROS PINHEIRO</t>
+  </si>
+  <si>
+    <t>2610 - ASSOCIAÇÃO DE GOVERNANÇA DOS A. DO ED. URBANO</t>
   </si>
 </sst>
 </file>
@@ -405,10 +408,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -731,7 +730,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="2" customWidth="1"/>
@@ -1465,6 +1464,23 @@
         <v>52</v>
       </c>
     </row>
+    <row r="35" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7">
+        <v>2610</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/AdmxEmprd.xlsx
+++ b/AdmxEmprd.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/matheus_almeida_osborne_com_br/Documents/Área de Trabalho/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="437" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A5CF938-EF98-406D-88C4-C340A4DAE72E}"/>
+  <xr:revisionPtr revIDLastSave="441" documentId="8_{B7F1CBA4-E6A5-4B28-B396-82823D345BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{594677CD-4317-435B-97FE-6CEBBF2F9E60}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CA07F2F2-64A9-422B-A346-649C5134B655}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="81">
   <si>
     <t>ADM</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>2610 - ASSOCIAÇÃO DE GOVERNANÇA DOS A. DO ED. URBANO</t>
+  </si>
+  <si>
+    <t>2613 - ODARA BRASIL LTDA</t>
   </si>
 </sst>
 </file>
@@ -408,6 +411,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -730,7 +737,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" style="2" customWidth="1"/>
@@ -1481,6 +1488,23 @@
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
     </row>
+    <row r="36" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7">
+        <v>2613</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
